--- a/vip-download/AI副業_実践How-To_運用シート集.xlsx
+++ b/vip-download/AI副業_実践How-To_運用シート集.xlsx
@@ -499,7 +499,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Ryu｜AI副業 実践How-To 同梱特典 ④｜あなたのジャンル（ブログ／note／X／Kindle／受注系PFほか）に当てはめて使う</t>
+          <t>Ryu｜AIコピペ副業の"全手順" 同梱特典 ④｜あなたのジャンル（ブログ／note／X／Kindle／受注系PFほか）に当てはめて使う</t>
         </is>
       </c>
     </row>
